--- a/questionnaire_templates/013_employee_involvement_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/013_employee_involvement_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>feedback_frequency</t>
+          <t>feedback_frequency_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Feedback Frequency</t>
+          <t>Feedback Frequency 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>feedback_urgency</t>
+          <t>feedback_urgency_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Feedback Urgency</t>
+          <t>Feedback Urgency 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>feedback_confidence</t>
+          <t>feedback_confidence_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Feedback Confidence</t>
+          <t>Feedback Confidence 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1572,7 +1572,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>feedback_frequency_choices</t>
+          <t>feedback_frequency_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1589,7 +1589,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>feedback_frequency_choices</t>
+          <t>feedback_frequency_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1606,7 +1606,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>feedback_frequency_choices</t>
+          <t>feedback_frequency_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1623,7 +1623,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>feedback_urgency_choices</t>
+          <t>feedback_urgency_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1640,7 +1640,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>feedback_urgency_choices</t>
+          <t>feedback_urgency_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>feedback_urgency_choices</t>
+          <t>feedback_urgency_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1674,7 +1674,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>feedback_confidence_choices</t>
+          <t>feedback_confidence_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1691,7 +1691,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>feedback_confidence_choices</t>
+          <t>feedback_confidence_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1708,7 +1708,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>feedback_confidence_choices</t>
+          <t>feedback_confidence_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
